--- a/Backtest/04-11-22/S&P500stock_04-11-22period252RS90.xlsx
+++ b/Backtest/04-11-22/S&P500stock_04-11-22period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="117">
   <si>
     <t>Stock</t>
   </si>
@@ -127,139 +127,196 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>MCK</t>
+    <t>EOG</t>
+  </si>
+  <si>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>CVX</t>
+  </si>
+  <si>
+    <t>MPC</t>
+  </si>
+  <si>
+    <t>OXY</t>
+  </si>
+  <si>
+    <t>DVN</t>
+  </si>
+  <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>HAL</t>
+  </si>
+  <si>
+    <t>CPT</t>
+  </si>
+  <si>
+    <t>VLO</t>
+  </si>
+  <si>
+    <t>NUE</t>
   </si>
   <si>
     <t>XOM</t>
   </si>
   <si>
-    <t>VLO</t>
-  </si>
-  <si>
-    <t>PSX</t>
-  </si>
-  <si>
     <t>FANG</t>
   </si>
   <si>
-    <t>PFG</t>
-  </si>
-  <si>
-    <t>CVX</t>
-  </si>
-  <si>
-    <t>COP</t>
+    <t>STLD</t>
+  </si>
+  <si>
+    <t>MOS</t>
+  </si>
+  <si>
+    <t>MAA</t>
+  </si>
+  <si>
+    <t>BKR</t>
+  </si>
+  <si>
+    <t>PLD</t>
+  </si>
+  <si>
+    <t>SLB</t>
+  </si>
+  <si>
+    <t>REGN</t>
+  </si>
+  <si>
+    <t>FCX</t>
+  </si>
+  <si>
+    <t>WMB</t>
+  </si>
+  <si>
+    <t>EXC</t>
+  </si>
+  <si>
+    <t>IRM</t>
   </si>
   <si>
     <t>HES</t>
   </si>
   <si>
-    <t>MPC</t>
-  </si>
-  <si>
-    <t>LW</t>
+    <t>PSA</t>
+  </si>
+  <si>
+    <t>ABBV</t>
+  </si>
+  <si>
+    <t>EXR</t>
+  </si>
+  <si>
+    <t>PANW</t>
   </si>
   <si>
     <t>APA</t>
   </si>
   <si>
-    <t>EOG</t>
-  </si>
-  <si>
-    <t>SLB</t>
-  </si>
-  <si>
-    <t>GWW</t>
-  </si>
-  <si>
-    <t>ENPH</t>
-  </si>
-  <si>
-    <t>TPL</t>
+    <t>PAYX</t>
   </si>
   <si>
     <t>ADM</t>
   </si>
   <si>
-    <t>GPC</t>
-  </si>
-  <si>
-    <t>VRTX</t>
-  </si>
-  <si>
-    <t>GIS</t>
-  </si>
-  <si>
-    <t>SMCI</t>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>CTRA</t>
   </si>
   <si>
     <t>M</t>
   </si>
   <si>
-    <t>2023-02-01</t>
-  </si>
-  <si>
-    <t>2023-01-31</t>
-  </si>
-  <si>
-    <t>2023-01-26</t>
-  </si>
-  <si>
-    <t>2022-11-07</t>
-  </si>
-  <si>
-    <t>2023-01-30</t>
-  </si>
-  <si>
-    <t>2023-01-27</t>
-  </si>
-  <si>
-    <t>2023-02-02</t>
-  </si>
-  <si>
-    <t>2023-01-25</t>
-  </si>
-  <si>
-    <t>2023-01-05</t>
-  </si>
-  <si>
-    <t>2023-02-22</t>
-  </si>
-  <si>
-    <t>2023-02-23</t>
-  </si>
-  <si>
-    <t>2023-01-20</t>
-  </si>
-  <si>
-    <t>2023-02-07</t>
-  </si>
-  <si>
-    <t>2022-12-20</t>
+    <t>2022-05-05</t>
+  </si>
+  <si>
+    <t>2022-04-20</t>
+  </si>
+  <si>
+    <t>2022-05-04</t>
+  </si>
+  <si>
+    <t>2022-04-29</t>
+  </si>
+  <si>
+    <t>2022-05-03</t>
+  </si>
+  <si>
+    <t>2022-05-10</t>
+  </si>
+  <si>
+    <t>2022-05-02</t>
+  </si>
+  <si>
+    <t>2022-04-19</t>
+  </si>
+  <si>
+    <t>2022-04-28</t>
+  </si>
+  <si>
+    <t>2022-04-26</t>
+  </si>
+  <si>
+    <t>2022-04-21</t>
+  </si>
+  <si>
+    <t>2022-04-27</t>
+  </si>
+  <si>
+    <t>2022-04-22</t>
+  </si>
+  <si>
+    <t>2022-05-09</t>
+  </si>
+  <si>
+    <t>2022-05-19</t>
+  </si>
+  <si>
+    <t>2022-06-29</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
+    <t>Basic Materials</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
   </si>
   <si>
     <t>Healthcare</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>Financial Services</t>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t>Technology</t>
   </si>
   <si>
     <t>Consumer Defensive</t>
   </si>
   <si>
-    <t>Industrials</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Consumer Cyclical</t>
-  </si>
-  <si>
-    <t>Medical Distribution</t>
+    <t>Oil &amp; Gas E&amp;P</t>
+  </si>
+  <si>
+    <t>Auto Manufacturers</t>
+  </si>
+  <si>
+    <t>Agricultural Inputs</t>
   </si>
   <si>
     <t>Oil &amp; Gas Integrated</t>
@@ -268,31 +325,43 @@
     <t>Oil &amp; Gas Refining &amp; Marketing</t>
   </si>
   <si>
-    <t>Oil &amp; Gas E&amp;P</t>
-  </si>
-  <si>
-    <t>Asset Management</t>
-  </si>
-  <si>
-    <t>Packaged Foods</t>
-  </si>
-  <si>
     <t>Oil &amp; Gas Equipment &amp; Services</t>
   </si>
   <si>
-    <t>Industrial Distribution</t>
-  </si>
-  <si>
-    <t>Solar</t>
+    <t>REIT - Residential</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+  <si>
+    <t>REIT - Industrial</t>
+  </si>
+  <si>
+    <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>Copper</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Midstream</t>
+  </si>
+  <si>
+    <t>Utilities - Regulated Electric</t>
+  </si>
+  <si>
+    <t>REIT - Specialty</t>
+  </si>
+  <si>
+    <t>Drug Manufacturers - General</t>
+  </si>
+  <si>
+    <t>Software - Infrastructure</t>
+  </si>
+  <si>
+    <t>Software - Application</t>
   </si>
   <si>
     <t>Farm Products</t>
-  </si>
-  <si>
-    <t>Auto Parts</t>
-  </si>
-  <si>
-    <t>Biotechnology</t>
   </si>
   <si>
     <t>Computer Hardware</t>
@@ -653,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK23"/>
+  <dimension ref="A1:AK37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -774,49 +843,49 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>98.39034205231388</v>
+        <v>97.58551307847083</v>
       </c>
       <c r="C2">
-        <v>373</v>
+        <v>194</v>
       </c>
       <c r="D2">
-        <v>397.58</v>
+        <v>126.88</v>
       </c>
       <c r="E2">
-        <v>1.49</v>
+        <v>2.55</v>
       </c>
       <c r="F2">
-        <v>-1.084494656999848</v>
+        <v>0.2381935582401788</v>
       </c>
       <c r="G2">
-        <v>1.47</v>
+        <v>2.4</v>
       </c>
       <c r="H2">
-        <v>-1.372350193542783</v>
+        <v>-0.07255307509294742</v>
       </c>
       <c r="I2">
-        <v>390.7</v>
+        <v>120.9220001220703</v>
       </c>
       <c r="J2">
-        <v>369.6220001220703</v>
+        <v>119.77200050354</v>
       </c>
       <c r="K2">
-        <v>359.8989996337891</v>
+        <v>116.1216000366211</v>
       </c>
       <c r="L2">
-        <v>323.5080499267578</v>
+        <v>91.90164989471435</v>
       </c>
       <c r="M2">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="P2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -825,7 +894,7 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>2.777777777777778</v>
+        <v>0</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
@@ -837,46 +906,46 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>215.27</v>
+        <v>62.81</v>
       </c>
       <c r="Y2">
-        <v>401.64</v>
+        <v>127.95</v>
       </c>
       <c r="Z2">
-        <v>48.98</v>
+        <v>51.88</v>
       </c>
       <c r="AA2">
-        <v>0.46</v>
+        <v>-43.12</v>
       </c>
       <c r="AB2">
-        <v>147.95</v>
+        <v>6076.92</v>
       </c>
       <c r="AC2">
-        <v>16275</v>
+        <v>192.31</v>
       </c>
       <c r="AD2">
-        <v>-77.90000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AE2">
-        <v>21.62</v>
+        <v>81.91</v>
       </c>
       <c r="AF2">
-        <v>111.11</v>
+        <v>20.51</v>
       </c>
       <c r="AG2">
-        <v>6400</v>
+        <v>33.33</v>
       </c>
       <c r="AH2" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="AI2" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="AJ2" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="AK2">
-        <v>75.0240551827509</v>
+        <v>82.26981155929548</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -884,112 +953,109 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>97.98792756539235</v>
+        <v>90.74446680080483</v>
       </c>
       <c r="C3">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>111.1</v>
+        <v>341.83</v>
       </c>
       <c r="E3">
-        <v>1.69</v>
+        <v>3.76</v>
       </c>
       <c r="F3">
-        <v>-0.8430079924857117</v>
+        <v>1.673285037761921</v>
       </c>
       <c r="G3">
-        <v>2.12</v>
+        <v>4.17</v>
       </c>
       <c r="H3">
-        <v>-0.4962516324864524</v>
+        <v>2.087765590758741</v>
       </c>
       <c r="I3">
-        <v>110.8259994506836</v>
+        <v>357.6813354492188</v>
       </c>
       <c r="J3">
-        <v>104.6830001831055</v>
+        <v>332.2850006103516</v>
       </c>
       <c r="K3">
-        <v>98.14199981689453</v>
+        <v>306.4161315917969</v>
       </c>
       <c r="L3">
-        <v>89.51794975280762</v>
+        <v>294.4812828826904</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N3">
-        <v>1.13</v>
-      </c>
-      <c r="O3" t="s">
-        <v>59</v>
+        <v>1.17</v>
       </c>
       <c r="P3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="T3">
-        <v>3.888888888888889</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
       <c r="V3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3">
-        <v>57.96</v>
+        <v>182.33</v>
       </c>
       <c r="Y3">
-        <v>112.91</v>
+        <v>414.5</v>
       </c>
       <c r="Z3">
-        <v>365.39</v>
+        <v>1192.75</v>
       </c>
       <c r="AA3">
-        <v>9.65</v>
+        <v>-186.33</v>
       </c>
       <c r="AB3">
-        <v>1675.36</v>
+        <v>363.53</v>
       </c>
       <c r="AC3">
-        <v>125</v>
+        <v>410.96</v>
       </c>
       <c r="AD3">
-        <v>10.46</v>
+        <v>7.55</v>
       </c>
       <c r="AE3">
-        <v>11.16</v>
+        <v>45.06</v>
       </c>
       <c r="AF3">
-        <v>228.91</v>
+        <v>37.3</v>
       </c>
       <c r="AG3">
-        <v>-38.46</v>
+        <v>156.56</v>
       </c>
       <c r="AH3" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="AI3" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="AJ3" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="AK3">
-        <v>69.70203373826284</v>
+        <v>69.11714929970402</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -997,61 +1063,61 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>97.58551307847083</v>
+        <v>99.19517102615694</v>
       </c>
       <c r="C4">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="D4">
-        <v>129.71</v>
+        <v>108.21</v>
       </c>
       <c r="E4">
-        <v>3.14</v>
+        <v>3.43</v>
       </c>
       <c r="F4">
-        <v>0.9077703252417767</v>
+        <v>1.28189645243781</v>
       </c>
       <c r="G4">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="H4">
-        <v>0.568545080182011</v>
+        <v>1.025914043136724</v>
       </c>
       <c r="I4">
-        <v>127.4140029907227</v>
+        <v>104.0639984130859</v>
       </c>
       <c r="J4">
-        <v>122.0975009918213</v>
+        <v>100.76549949646</v>
       </c>
       <c r="K4">
-        <v>115.6118000793457</v>
+        <v>87.94619979858399</v>
       </c>
       <c r="L4">
-        <v>108.4289499282837</v>
+        <v>64.52190002441407</v>
       </c>
       <c r="M4">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N4">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="P4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>2.222222222222222</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="U4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="b">
         <v>1</v>
@@ -1060,46 +1126,46 @@
         <v>1</v>
       </c>
       <c r="X4">
-        <v>65.13</v>
+        <v>43.19</v>
       </c>
       <c r="Y4">
-        <v>146.81</v>
+        <v>110.4</v>
       </c>
       <c r="Z4">
-        <v>41.67</v>
+        <v>15.3</v>
       </c>
       <c r="AA4">
-        <v>4.7</v>
+        <v>-51.32</v>
       </c>
       <c r="AB4">
-        <v>1600.72</v>
+        <v>95.87</v>
       </c>
       <c r="AC4">
-        <v>190.32</v>
+        <v>370</v>
       </c>
       <c r="AD4">
-        <v>12.28</v>
+        <v>14.23</v>
       </c>
       <c r="AE4">
-        <v>-37.82</v>
+        <v>482.56</v>
       </c>
       <c r="AF4">
-        <v>423.98</v>
+        <v>-175.44</v>
       </c>
       <c r="AG4">
-        <v>-10.89</v>
+        <v>62.86</v>
       </c>
       <c r="AH4" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="AI4" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="AJ4" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="AK4">
-        <v>69.2468208958293</v>
+        <v>68.29192612050147</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1107,43 +1173,43 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>91.95171026156942</v>
+        <v>96.37826961770624</v>
       </c>
       <c r="C5">
-        <v>174</v>
+        <v>60</v>
       </c>
       <c r="D5">
-        <v>103.12</v>
+        <v>169.93</v>
       </c>
       <c r="E5">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="F5">
-        <v>-0.4566293292630939</v>
+        <v>-0.7224875148280946</v>
       </c>
       <c r="G5">
-        <v>2.61</v>
+        <v>1.91</v>
       </c>
       <c r="H5">
-        <v>0.1641918981560119</v>
+        <v>-0.6706073950179909</v>
       </c>
       <c r="I5">
-        <v>104.4459991455078</v>
+        <v>165.9139984130859</v>
       </c>
       <c r="J5">
-        <v>98.7129997253418</v>
+        <v>164.3925003051758</v>
       </c>
       <c r="K5">
-        <v>90.75860000610352</v>
+        <v>151.9285998535156</v>
       </c>
       <c r="L5">
-        <v>88.69750007629395</v>
+        <v>119.7922499847412</v>
       </c>
       <c r="M5">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1161,55 +1227,55 @@
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5">
-        <v>67.08</v>
+        <v>92.86</v>
       </c>
       <c r="Y5">
-        <v>111.28</v>
+        <v>174.76</v>
       </c>
       <c r="Z5">
-        <v>38.99</v>
+        <v>225.31</v>
       </c>
       <c r="AA5">
-        <v>4.21</v>
+        <v>121.14</v>
       </c>
       <c r="AB5">
-        <v>1174.42</v>
+        <v>463.84</v>
       </c>
       <c r="AC5">
-        <v>287.2</v>
+        <v>265.28</v>
       </c>
       <c r="AD5">
-        <v>16.63</v>
+        <v>3.63</v>
       </c>
       <c r="AE5">
-        <v>70.84</v>
+        <v>-17.55</v>
       </c>
       <c r="AF5">
-        <v>407.75</v>
+        <v>98.14</v>
       </c>
       <c r="AG5">
-        <v>-55.36</v>
+        <v>123.61</v>
       </c>
       <c r="AH5" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="AI5" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ5" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="AK5">
-        <v>65.92839734074315</v>
+        <v>66.78449528232775</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1217,49 +1283,46 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>94.56740442655935</v>
+        <v>95.97585513078471</v>
       </c>
       <c r="C6">
-        <v>294</v>
+        <v>140</v>
       </c>
       <c r="D6">
-        <v>158.53</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="E6">
-        <v>1.93</v>
+        <v>1.52</v>
       </c>
       <c r="F6">
-        <v>-0.5532239950687482</v>
+        <v>-0.9834132383775022</v>
       </c>
       <c r="G6">
-        <v>2.78</v>
+        <v>1.87</v>
       </c>
       <c r="H6">
-        <v>0.3933253679707444</v>
+        <v>-0.7194281558281984</v>
       </c>
       <c r="I6">
-        <v>156.5840026855469</v>
+        <v>85.61999969482422</v>
       </c>
       <c r="J6">
-        <v>148.6220008850098</v>
+        <v>81.67850036621094</v>
       </c>
       <c r="K6">
-        <v>137.819400177002</v>
+        <v>78.88400054931641</v>
       </c>
       <c r="L6">
-        <v>132.9641500091553</v>
+        <v>66.3168002128601</v>
       </c>
       <c r="M6">
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>1.14</v>
-      </c>
-      <c r="O6" t="s">
-        <v>59</v>
+        <v>1.09</v>
       </c>
       <c r="P6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -1268,13 +1331,13 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>7.222222222222221</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="U6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="b">
         <v>1</v>
@@ -1283,46 +1346,46 @@
         <v>1</v>
       </c>
       <c r="X6">
-        <v>95.02</v>
+        <v>50.19</v>
       </c>
       <c r="Y6">
-        <v>162.24</v>
+        <v>87.67</v>
       </c>
       <c r="Z6">
-        <v>21.39</v>
+        <v>40.83</v>
       </c>
       <c r="AA6">
-        <v>23.9</v>
+        <v>59.02</v>
       </c>
       <c r="AB6">
-        <v>517.9</v>
+        <v>198.97</v>
       </c>
       <c r="AC6">
-        <v>123.38</v>
+        <v>510.81</v>
       </c>
       <c r="AD6">
-        <v>10.15</v>
+        <v>3.39</v>
       </c>
       <c r="AE6">
-        <v>82.3</v>
+        <v>38.18</v>
       </c>
       <c r="AF6">
-        <v>-23.01</v>
+        <v>-91.59999999999999</v>
       </c>
       <c r="AG6">
-        <v>59.15</v>
+        <v>3637.84</v>
       </c>
       <c r="AH6" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="AI6" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ6" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="AK6">
-        <v>65.13125161774053</v>
+        <v>66.4964996815817</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1330,58 +1393,58 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>90.74446680080483</v>
+        <v>99.79879275653923</v>
       </c>
       <c r="C7">
-        <v>267</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>86.51000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="E7">
-        <v>2.35</v>
+        <v>4.03</v>
       </c>
       <c r="F7">
-        <v>-0.04610199958906174</v>
+        <v>1.993512062118012</v>
       </c>
       <c r="G7">
-        <v>1.99</v>
+        <v>4.2</v>
       </c>
       <c r="H7">
-        <v>-0.6714713446977186</v>
+        <v>2.124381161366397</v>
       </c>
       <c r="I7">
-        <v>87.5520004272461</v>
+        <v>57.81800003051758</v>
       </c>
       <c r="J7">
-        <v>80.6609992980957</v>
+        <v>57.45550003051758</v>
       </c>
       <c r="K7">
-        <v>77.72059997558594</v>
+        <v>49.3907999420166</v>
       </c>
       <c r="L7">
-        <v>72.31895004272461</v>
+        <v>34.66275000572205</v>
       </c>
       <c r="M7">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="P7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7">
         <v>1</v>
       </c>
       <c r="T7">
-        <v>2.222222222222222</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -1390,49 +1453,49 @@
         <v>1</v>
       </c>
       <c r="W7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>61.05</v>
+        <v>21.62</v>
       </c>
       <c r="Y7">
-        <v>89.27</v>
+        <v>63.24</v>
       </c>
       <c r="Z7">
-        <v>18.17</v>
+        <v>27.8</v>
       </c>
       <c r="AA7">
-        <v>4.88</v>
+        <v>-90</v>
       </c>
       <c r="AB7">
-        <v>167.06</v>
+        <v>109.29</v>
       </c>
       <c r="AC7">
-        <v>308.46</v>
+        <v>483.78</v>
       </c>
       <c r="AD7">
-        <v>13.82</v>
+        <v>14.78</v>
       </c>
       <c r="AE7">
-        <v>-57</v>
+        <v>111.94</v>
       </c>
       <c r="AF7">
-        <v>842.75</v>
+        <v>770</v>
       </c>
       <c r="AG7">
-        <v>0.77</v>
+        <v>72.97</v>
       </c>
       <c r="AH7" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="AI7" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ7" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="AK7">
-        <v>54.25801370303866</v>
+        <v>66.29846419741547</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1440,112 +1503,109 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>96.98189134808854</v>
+        <v>100</v>
       </c>
       <c r="C8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D8">
-        <v>181.13</v>
+        <v>62.37</v>
       </c>
       <c r="E8">
-        <v>1.78</v>
+        <v>3.93</v>
       </c>
       <c r="F8">
-        <v>-0.7343389934543503</v>
+        <v>1.874909460504645</v>
       </c>
       <c r="G8">
-        <v>2.03</v>
+        <v>3.18</v>
       </c>
       <c r="H8">
-        <v>-0.6175575870942523</v>
+        <v>0.8794517607061018</v>
       </c>
       <c r="I8">
-        <v>180.5459991455078</v>
+        <v>60.05199966430664</v>
       </c>
       <c r="J8">
-        <v>169.8679992675781</v>
+        <v>59.14949970245361</v>
       </c>
       <c r="K8">
-        <v>161.3169995117188</v>
+        <v>56.68279960632324</v>
       </c>
       <c r="L8">
-        <v>157.1087498855591</v>
+        <v>41.5425999546051</v>
       </c>
       <c r="M8">
+        <v>1.02</v>
+      </c>
+      <c r="N8">
         <v>1.06</v>
       </c>
-      <c r="N8">
-        <v>1.12</v>
-      </c>
-      <c r="O8" t="s">
-        <v>59</v>
-      </c>
       <c r="P8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
       <c r="T8">
-        <v>5.555555555555555</v>
+        <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
       </c>
       <c r="W8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8">
-        <v>110.73</v>
+        <v>20.14</v>
       </c>
       <c r="Y8">
-        <v>184.5</v>
+        <v>63.26</v>
       </c>
       <c r="Z8">
-        <v>278.72</v>
+        <v>29.29</v>
       </c>
       <c r="AA8">
-        <v>13.57</v>
+        <v>-36.84</v>
       </c>
       <c r="AB8">
-        <v>125.7</v>
+        <v>161.86</v>
       </c>
       <c r="AC8">
-        <v>120.91</v>
+        <v>581.8200000000001</v>
       </c>
       <c r="AD8">
-        <v>7.04</v>
+        <v>16.09</v>
       </c>
       <c r="AE8">
-        <v>-2.84</v>
+        <v>81.45</v>
       </c>
       <c r="AF8">
-        <v>85.14</v>
+        <v>226.32</v>
       </c>
       <c r="AG8">
-        <v>22.81</v>
+        <v>15.15</v>
       </c>
       <c r="AH8" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AI8" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ8" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="AK8">
-        <v>51.75533988513023</v>
+        <v>65.0385399019988</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1553,58 +1613,58 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>98.79275653923541</v>
+        <v>98.59154929577466</v>
       </c>
       <c r="C9">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="D9">
-        <v>133.82</v>
+        <v>103.05</v>
       </c>
       <c r="E9">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="F9">
-        <v>-0.1547709986204235</v>
+        <v>-0.1531950270839322</v>
       </c>
       <c r="G9">
-        <v>2.61</v>
+        <v>2.15</v>
       </c>
       <c r="H9">
-        <v>0.1641918981560119</v>
+        <v>-0.3776828301567451</v>
       </c>
       <c r="I9">
-        <v>128.2740005493164</v>
+        <v>99.83000183105467</v>
       </c>
       <c r="J9">
-        <v>122.7605003356934</v>
+        <v>100.5405010223389</v>
       </c>
       <c r="K9">
-        <v>115.0436000061035</v>
+        <v>96.14060089111328</v>
       </c>
       <c r="L9">
-        <v>102.0442500686646</v>
+        <v>74.49610010147094</v>
       </c>
       <c r="M9">
+        <v>0.99</v>
+      </c>
+      <c r="N9">
         <v>1.04</v>
       </c>
-      <c r="N9">
-        <v>1.12</v>
-      </c>
       <c r="P9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9">
         <v>0</v>
       </c>
       <c r="R9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>5.555555555555556</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
@@ -1613,49 +1673,49 @@
         <v>1</v>
       </c>
       <c r="W9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9">
-        <v>66.06</v>
+        <v>47.85</v>
       </c>
       <c r="Y9">
-        <v>136.12</v>
+        <v>107.52</v>
       </c>
       <c r="Z9">
-        <v>129.9</v>
+        <v>95.87</v>
       </c>
       <c r="AA9">
-        <v>-523.9299999999999</v>
+        <v>-20.46</v>
       </c>
       <c r="AB9">
-        <v>160.45</v>
+        <v>446.02</v>
       </c>
       <c r="AC9">
-        <v>77.11</v>
+        <v>168</v>
       </c>
       <c r="AD9">
-        <v>9.220000000000001</v>
+        <v>5.79</v>
       </c>
       <c r="AE9">
-        <v>-10.55</v>
+        <v>12.92</v>
       </c>
       <c r="AF9">
-        <v>-9.75</v>
+        <v>14.84</v>
       </c>
       <c r="AG9">
-        <v>119.4</v>
+        <v>106.67</v>
       </c>
       <c r="AH9" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="AI9" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ9" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="AK9">
-        <v>51.28795244612494</v>
+        <v>63.33026711877594</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1666,40 +1726,40 @@
         <v>98.18913480885311</v>
       </c>
       <c r="C10">
-        <v>255</v>
+        <v>57</v>
       </c>
       <c r="D10">
-        <v>142.1</v>
+        <v>39.94</v>
       </c>
       <c r="E10">
-        <v>2.29</v>
+        <v>3.01</v>
       </c>
       <c r="F10">
-        <v>-0.1185479989433027</v>
+        <v>0.7837655256616674</v>
       </c>
       <c r="G10">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="H10">
-        <v>0.5955019589837443</v>
+        <v>0.5987323860474079</v>
       </c>
       <c r="I10">
-        <v>141.4700012207031</v>
+        <v>38.26799926757813</v>
       </c>
       <c r="J10">
-        <v>133.2689998626709</v>
+        <v>37.39449996948242</v>
       </c>
       <c r="K10">
-        <v>124.5341996765137</v>
+        <v>34.77699996948243</v>
       </c>
       <c r="L10">
-        <v>110.5361998748779</v>
+        <v>25.77449996948242</v>
       </c>
       <c r="M10">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N10">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -1726,46 +1786,46 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>68.31999999999999</v>
+        <v>17.82</v>
       </c>
       <c r="Y10">
-        <v>147.52</v>
+        <v>40</v>
       </c>
       <c r="Z10">
-        <v>33.67</v>
+        <v>20.4</v>
       </c>
       <c r="AA10">
-        <v>-0.14</v>
+        <v>-0.72</v>
       </c>
       <c r="AB10">
-        <v>297.37</v>
+        <v>151.75</v>
       </c>
       <c r="AC10">
-        <v>91.95</v>
+        <v>384.21</v>
       </c>
       <c r="AD10">
-        <v>7.4</v>
+        <v>12.29</v>
       </c>
       <c r="AE10">
-        <v>-22.33</v>
+        <v>253.85</v>
       </c>
       <c r="AF10">
-        <v>59.26</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>55.17</v>
+        <v>36.84</v>
       </c>
       <c r="AH10" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="AI10" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ10" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="AK10">
-        <v>49.28971225723517</v>
+        <v>61.69602145973212</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1773,49 +1833,49 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>98.99396378269618</v>
+        <v>92.15291750503019</v>
       </c>
       <c r="C11">
-        <v>184</v>
+        <v>330</v>
       </c>
       <c r="D11">
-        <v>118.2</v>
+        <v>168.21</v>
       </c>
       <c r="E11">
-        <v>2.34</v>
+        <v>1.67</v>
       </c>
       <c r="F11">
-        <v>-0.05817633281476884</v>
+        <v>-0.8055093359574516</v>
       </c>
       <c r="G11">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="H11">
-        <v>-0.18624752626652</v>
+        <v>-0.9025060088664771</v>
       </c>
       <c r="I11">
-        <v>115.8639999389649</v>
+        <v>170.9860046386719</v>
       </c>
       <c r="J11">
-        <v>110.3284999847412</v>
+        <v>167.5430015563965</v>
       </c>
       <c r="K11">
-        <v>103.7007998657227</v>
+        <v>165.8526007080078</v>
       </c>
       <c r="L11">
-        <v>91.39540019989013</v>
+        <v>158.6369500732422</v>
       </c>
       <c r="M11">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N11">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="P11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -1824,58 +1884,58 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>1.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="U11" t="b">
         <v>0</v>
       </c>
       <c r="V11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11">
-        <v>59.55</v>
+        <v>111.57</v>
       </c>
       <c r="Y11">
-        <v>119.84</v>
+        <v>180.37</v>
       </c>
       <c r="Z11">
-        <v>49.07</v>
+        <v>18.37</v>
       </c>
       <c r="AA11">
-        <v>8.970000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="AB11">
-        <v>46.55</v>
+        <v>91.61</v>
       </c>
       <c r="AC11">
-        <v>500</v>
+        <v>567.74</v>
       </c>
       <c r="AD11">
-        <v>15.3</v>
+        <v>5.11</v>
       </c>
       <c r="AE11">
-        <v>-17.32</v>
+        <v>613.79</v>
       </c>
       <c r="AF11">
-        <v>635.33</v>
+        <v>-3.33</v>
       </c>
       <c r="AG11">
-        <v>-1.32</v>
+        <v>-3.23</v>
       </c>
       <c r="AH11" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="AJ11" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="AK11">
-        <v>46.21755145630428</v>
+        <v>60.9743048564886</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1883,49 +1943,49 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>95.17102615694165</v>
+        <v>91.14688128772636</v>
       </c>
       <c r="C12">
-        <v>364</v>
+        <v>161</v>
       </c>
       <c r="D12">
-        <v>84.86</v>
+        <v>103.22</v>
       </c>
       <c r="E12">
-        <v>1.31</v>
+        <v>2.43</v>
       </c>
       <c r="F12">
-        <v>-1.301832655062571</v>
+        <v>0.09587043630413865</v>
       </c>
       <c r="G12">
-        <v>1.45</v>
+        <v>2.43</v>
       </c>
       <c r="H12">
-        <v>-1.399307072344516</v>
+        <v>-0.03593750448529139</v>
       </c>
       <c r="I12">
-        <v>85.78000030517578</v>
+        <v>102.4100006103516</v>
       </c>
       <c r="J12">
-        <v>84.10099983215332</v>
+        <v>96.24450035095215</v>
       </c>
       <c r="K12">
-        <v>80.91119979858398</v>
+        <v>90.49780014038086</v>
       </c>
       <c r="L12">
-        <v>70.73804992675781</v>
+        <v>76.66119998931885</v>
       </c>
       <c r="M12">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N12">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1934,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="U12" t="b">
         <v>0</v>
@@ -1943,49 +2003,49 @@
         <v>1</v>
       </c>
       <c r="W12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>49.71</v>
+        <v>58.85</v>
       </c>
       <c r="Y12">
-        <v>88.04000000000001</v>
+        <v>104.76</v>
       </c>
       <c r="Z12">
-        <v>11.5</v>
+        <v>30.57</v>
       </c>
       <c r="AA12">
-        <v>7.33</v>
+        <v>1.44</v>
       </c>
       <c r="AB12">
-        <v>40.2</v>
+        <v>143.4</v>
       </c>
       <c r="AC12">
-        <v>600</v>
+        <v>243.35</v>
       </c>
       <c r="AD12">
-        <v>45.47</v>
+        <v>5.6</v>
       </c>
       <c r="AE12">
-        <v>631.8200000000001</v>
+        <v>119.47</v>
       </c>
       <c r="AF12">
-        <v>-69.86</v>
+        <v>189.74</v>
       </c>
       <c r="AG12">
-        <v>217.39</v>
+        <v>122.54</v>
       </c>
       <c r="AH12" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="AI12" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="AJ12" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AK12">
-        <v>43.75681286290721</v>
+        <v>60.50087900170251</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -1993,40 +2053,40 @@
         <v>48</v>
       </c>
       <c r="B13">
-        <v>97.78672032193158</v>
+        <v>97.98792756539235</v>
       </c>
       <c r="C13">
-        <v>95</v>
+        <v>211</v>
       </c>
       <c r="D13">
-        <v>47.29</v>
+        <v>150.76</v>
       </c>
       <c r="E13">
+        <v>2.12</v>
+      </c>
+      <c r="F13">
+        <v>-0.2717976286972995</v>
+      </c>
+      <c r="G13">
         <v>2.88</v>
       </c>
-      <c r="F13">
-        <v>0.5938376613733992</v>
-      </c>
-      <c r="G13">
-        <v>3.7</v>
-      </c>
       <c r="H13">
-        <v>1.633341792850474</v>
+        <v>0.5132960546295442</v>
       </c>
       <c r="I13">
-        <v>45.64400024414063</v>
+        <v>149.2960021972656</v>
       </c>
       <c r="J13">
-        <v>43.11149978637695</v>
+        <v>145.8505004882813</v>
       </c>
       <c r="K13">
-        <v>40.15199989318847</v>
+        <v>131.491600189209</v>
       </c>
       <c r="L13">
-        <v>38.69319995880127</v>
+        <v>113.4332998275757</v>
       </c>
       <c r="M13">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N13">
         <v>1.14</v>
@@ -2047,55 +2107,55 @@
         <v>0</v>
       </c>
       <c r="U13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" t="b">
         <v>1</v>
       </c>
       <c r="W13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>22.94</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="Y13">
-        <v>51.95</v>
+        <v>157.69</v>
       </c>
       <c r="Z13">
-        <v>11.28</v>
+        <v>33.49</v>
       </c>
       <c r="AA13">
-        <v>24.27</v>
+        <v>36.05</v>
       </c>
       <c r="AB13">
-        <v>298.86</v>
+        <v>324.68</v>
       </c>
       <c r="AC13">
-        <v>21.9</v>
+        <v>151.29</v>
       </c>
       <c r="AD13">
-        <v>34.17</v>
+        <v>16.02</v>
       </c>
       <c r="AE13">
-        <v>-52.94</v>
+        <v>6.86</v>
       </c>
       <c r="AF13">
-        <v>-50</v>
+        <v>44.36</v>
       </c>
       <c r="AG13">
-        <v>418.1</v>
+        <v>62.9</v>
       </c>
       <c r="AH13" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="AI13" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="AJ13" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="AK13">
-        <v>41.9270562415951</v>
+        <v>60.41701473830908</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2103,61 +2163,61 @@
         <v>49</v>
       </c>
       <c r="B14">
-        <v>96.579476861167</v>
+        <v>93.96378269617706</v>
       </c>
       <c r="C14">
-        <v>152</v>
+        <v>23</v>
       </c>
       <c r="D14">
-        <v>138.38</v>
+        <v>86.84</v>
       </c>
       <c r="E14">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="F14">
-        <v>-0.1306223321690098</v>
+        <v>-0.03459242547056555</v>
       </c>
       <c r="G14">
-        <v>2.68</v>
+        <v>2.15</v>
       </c>
       <c r="H14">
-        <v>0.2585409739620786</v>
+        <v>-0.3776828301567451</v>
       </c>
       <c r="I14">
-        <v>136.0980010986328</v>
+        <v>84.28600158691407</v>
       </c>
       <c r="J14">
-        <v>130.1294998168945</v>
+        <v>82.27649955749511</v>
       </c>
       <c r="K14">
-        <v>123.8619999694824</v>
+        <v>80.96819976806641</v>
       </c>
       <c r="L14">
-        <v>118.4586000061035</v>
+        <v>66.12299983978272</v>
       </c>
       <c r="M14">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N14">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="P14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q14">
         <v>0</v>
       </c>
       <c r="R14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
       <c r="T14">
-        <v>2.777777777777778</v>
+        <v>0</v>
       </c>
       <c r="U14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" t="b">
         <v>1</v>
@@ -2166,46 +2226,46 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>80.67</v>
+        <v>52.1</v>
       </c>
       <c r="Y14">
-        <v>147.99</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="Z14">
-        <v>65.59</v>
+        <v>261.59</v>
       </c>
       <c r="AA14">
-        <v>14.21</v>
+        <v>13.46</v>
       </c>
       <c r="AB14">
-        <v>49.01</v>
+        <v>216.92</v>
       </c>
       <c r="AC14">
-        <v>43.27</v>
+        <v>225</v>
       </c>
       <c r="AD14">
-        <v>11.97</v>
+        <v>5.17</v>
       </c>
       <c r="AE14">
-        <v>27.6</v>
+        <v>32.48</v>
       </c>
       <c r="AF14">
-        <v>473.13</v>
+        <v>42.73</v>
       </c>
       <c r="AG14">
-        <v>-80.41</v>
+        <v>71.88</v>
       </c>
       <c r="AH14" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="AI14" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ14" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="AK14">
-        <v>35.32954675366105</v>
+        <v>60.41122117587732</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2213,43 +2273,43 @@
         <v>50</v>
       </c>
       <c r="B15">
-        <v>96.78068410462777</v>
+        <v>98.39034205231388</v>
       </c>
       <c r="C15">
-        <v>40</v>
+        <v>281</v>
       </c>
       <c r="D15">
-        <v>51.8</v>
+        <v>141.99</v>
       </c>
       <c r="E15">
-        <v>3.21</v>
+        <v>2.92</v>
       </c>
       <c r="F15">
-        <v>0.9922906578217242</v>
+        <v>0.6770231842096371</v>
       </c>
       <c r="G15">
-        <v>3.31</v>
+        <v>2.71</v>
       </c>
       <c r="H15">
-        <v>1.107682656216676</v>
+        <v>0.3058078211861618</v>
       </c>
       <c r="I15">
-        <v>51.39399948120117</v>
+        <v>137.8139984130859</v>
       </c>
       <c r="J15">
-        <v>47.40450000762939</v>
+        <v>136.7224994659424</v>
       </c>
       <c r="K15">
-        <v>41.87640014648437</v>
+        <v>133.5130006408691</v>
       </c>
       <c r="L15">
-        <v>40.11280005455017</v>
+        <v>106.6990504455566</v>
       </c>
       <c r="M15">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2258,13 +2318,13 @@
         <v>0</v>
       </c>
       <c r="R15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>4.444444444444444</v>
+        <v>0</v>
       </c>
       <c r="U15" t="b">
         <v>1</v>
@@ -2276,46 +2336,46 @@
         <v>1</v>
       </c>
       <c r="X15">
-        <v>27.65</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="Y15">
-        <v>53.89</v>
+        <v>147.99</v>
       </c>
       <c r="Z15">
-        <v>51.66</v>
+        <v>19.05</v>
       </c>
       <c r="AA15">
-        <v>-25.36</v>
+        <v>-447.04</v>
       </c>
       <c r="AB15">
-        <v>30.25</v>
+        <v>144.88</v>
       </c>
       <c r="AC15">
-        <v>48.84</v>
+        <v>321.64</v>
       </c>
       <c r="AD15">
-        <v>5.25</v>
+        <v>7.94</v>
       </c>
       <c r="AE15">
-        <v>-5.88</v>
+        <v>59.15</v>
       </c>
       <c r="AF15">
-        <v>88.89</v>
+        <v>108.82</v>
       </c>
       <c r="AG15">
-        <v>-16.28</v>
+        <v>26.87</v>
       </c>
       <c r="AH15" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ15" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AK15">
-        <v>34.60740337036638</v>
+        <v>60.13708399003179</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2323,109 +2383,109 @@
         <v>51</v>
       </c>
       <c r="B16">
-        <v>91.14688128772636</v>
+        <v>94.96981891348088</v>
       </c>
       <c r="C16">
-        <v>482</v>
+        <v>296</v>
       </c>
       <c r="D16">
-        <v>594.4</v>
+        <v>83.2</v>
       </c>
       <c r="E16">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="F16">
-        <v>0.00219533331376556</v>
+        <v>0.3330756395308725</v>
       </c>
       <c r="G16">
-        <v>1.92</v>
+        <v>2.94</v>
       </c>
       <c r="H16">
-        <v>-0.7658204205037851</v>
+        <v>0.5865271958448557</v>
       </c>
       <c r="I16">
-        <v>586.2619995117187</v>
+        <v>83.02999877929688</v>
       </c>
       <c r="J16">
-        <v>534.9899993896485</v>
+        <v>82.82049942016602</v>
       </c>
       <c r="K16">
-        <v>534.6869995117188</v>
+        <v>72.21139961242676</v>
       </c>
       <c r="L16">
-        <v>504.9109489440918</v>
+        <v>65.07274993896485</v>
       </c>
       <c r="M16">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="N16">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="P16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q16">
         <v>0</v>
       </c>
       <c r="R16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>5.555555555555555</v>
+        <v>0</v>
       </c>
       <c r="U16" t="b">
         <v>0</v>
       </c>
       <c r="V16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16">
-        <v>440.48</v>
+        <v>49.53</v>
       </c>
       <c r="Y16">
-        <v>603.09</v>
+        <v>89.69</v>
       </c>
       <c r="Z16">
-        <v>25</v>
+        <v>12.82</v>
       </c>
       <c r="AA16">
-        <v>4.54</v>
+        <v>54.41</v>
       </c>
       <c r="AB16">
-        <v>21.71</v>
+        <v>236.99</v>
       </c>
       <c r="AC16">
-        <v>52.48</v>
+        <v>164.22</v>
       </c>
       <c r="AD16">
-        <v>17.25</v>
+        <v>17.94</v>
       </c>
       <c r="AE16">
-        <v>15.1</v>
+        <v>10.22</v>
       </c>
       <c r="AF16">
-        <v>1.55</v>
+        <v>45.97</v>
       </c>
       <c r="AG16">
-        <v>30.46</v>
+        <v>64.22</v>
       </c>
       <c r="AH16" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="AI16" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="AJ16" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="AK16">
-        <v>34.03630777869336</v>
+        <v>58.82454362821164</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2433,43 +2493,43 @@
         <v>52</v>
       </c>
       <c r="B17">
-        <v>90.94567404426559</v>
+        <v>98.99396378269618</v>
       </c>
       <c r="C17">
-        <v>213</v>
+        <v>56</v>
       </c>
       <c r="D17">
-        <v>296.11</v>
+        <v>73.86</v>
       </c>
       <c r="E17">
-        <v>3.45</v>
+        <v>3.63</v>
       </c>
       <c r="F17">
-        <v>1.282074655238688</v>
+        <v>1.519101655664544</v>
       </c>
       <c r="G17">
-        <v>3.34</v>
+        <v>3.49</v>
       </c>
       <c r="H17">
-        <v>1.148117974419276</v>
+        <v>1.257812656985211</v>
       </c>
       <c r="I17">
-        <v>299.4679992675781</v>
+        <v>69.86399993896484</v>
       </c>
       <c r="J17">
-        <v>267.5599975585938</v>
+        <v>65.88199920654297</v>
       </c>
       <c r="K17">
-        <v>282.8983990478516</v>
+        <v>55.70659950256348</v>
       </c>
       <c r="L17">
-        <v>214.1946998596191</v>
+        <v>40.68904998779297</v>
       </c>
       <c r="M17">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="N17">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -2493,49 +2553,49 @@
         <v>1</v>
       </c>
       <c r="W17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>113.4</v>
+        <v>28.26</v>
       </c>
       <c r="Y17">
-        <v>324.84</v>
+        <v>74.75</v>
       </c>
       <c r="Z17">
-        <v>40.5</v>
+        <v>14.99</v>
       </c>
       <c r="AA17">
-        <v>-87.68000000000001</v>
+        <v>120.04</v>
       </c>
       <c r="AB17">
-        <v>32.34</v>
+        <v>98.62</v>
       </c>
       <c r="AC17">
-        <v>112.5</v>
+        <v>331.71</v>
       </c>
       <c r="AD17">
-        <v>18.82</v>
+        <v>6.15</v>
       </c>
       <c r="AE17">
-        <v>49.12</v>
+        <v>80.61</v>
       </c>
       <c r="AF17">
-        <v>46.15</v>
+        <v>-14.78</v>
       </c>
       <c r="AG17">
-        <v>-2.5</v>
+        <v>180.49</v>
       </c>
       <c r="AH17" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="AI17" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="AJ17" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="AK17">
-        <v>33.3049223583007</v>
+        <v>57.72195595287916</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2543,43 +2603,43 @@
         <v>53</v>
       </c>
       <c r="B18">
-        <v>99.19517102615694</v>
+        <v>90.54325955734407</v>
       </c>
       <c r="C18">
-        <v>494</v>
+        <v>422</v>
       </c>
       <c r="D18">
-        <v>798.41</v>
+        <v>214.33</v>
       </c>
       <c r="E18">
-        <v>2.67</v>
+        <v>1.28</v>
       </c>
       <c r="F18">
-        <v>0.3402766636335561</v>
+        <v>-1.268059482249583</v>
       </c>
       <c r="G18">
-        <v>3.23</v>
+        <v>1.57</v>
       </c>
       <c r="H18">
-        <v>0.9998551410097427</v>
+        <v>-1.085583861904756</v>
       </c>
       <c r="I18">
-        <v>779.2993286132812</v>
+        <v>213.9620025634766</v>
       </c>
       <c r="J18">
-        <v>714.6924926757813</v>
+        <v>209.568000793457</v>
       </c>
       <c r="K18">
-        <v>648.1814636230469</v>
+        <v>209.0492004394531</v>
       </c>
       <c r="L18">
-        <v>520.2199166870117</v>
+        <v>200.9726499176026</v>
       </c>
       <c r="M18">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="N18">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -2597,55 +2657,55 @@
         <v>0</v>
       </c>
       <c r="U18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="b">
         <v>1</v>
       </c>
       <c r="W18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18">
-        <v>315.43</v>
+        <v>146.61</v>
       </c>
       <c r="Y18">
-        <v>830.97</v>
+        <v>231.63</v>
       </c>
       <c r="Z18">
-        <v>13.72</v>
+        <v>26.39</v>
       </c>
       <c r="AA18">
-        <v>15.95</v>
+        <v>9.93</v>
       </c>
       <c r="AB18">
-        <v>35.59</v>
+        <v>77.69</v>
       </c>
       <c r="AC18">
-        <v>65</v>
+        <v>302.5</v>
       </c>
       <c r="AD18">
-        <v>18</v>
+        <v>3.1</v>
       </c>
       <c r="AE18">
-        <v>9.5</v>
+        <v>120.55</v>
       </c>
       <c r="AF18">
-        <v>21.5</v>
+        <v>-61.17</v>
       </c>
       <c r="AG18">
-        <v>24.02</v>
+        <v>370</v>
       </c>
       <c r="AH18" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="AI18" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="AJ18" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="AK18">
-        <v>31.16386887631074</v>
+        <v>55.45182508416202</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2653,109 +2713,109 @@
         <v>54</v>
       </c>
       <c r="B19">
-        <v>95.37223340040242</v>
+        <v>97.78672032193158</v>
       </c>
       <c r="C19">
-        <v>234</v>
+        <v>49</v>
       </c>
       <c r="D19">
-        <v>96.28</v>
+        <v>37.52</v>
       </c>
       <c r="E19">
-        <v>2.07</v>
+        <v>2.7</v>
       </c>
       <c r="F19">
-        <v>-0.3841833299088529</v>
+        <v>0.4160974606602298</v>
       </c>
       <c r="G19">
+        <v>2.88</v>
+      </c>
+      <c r="H19">
+        <v>0.5132960546295442</v>
+      </c>
+      <c r="I19">
+        <v>36.26200027465821</v>
+      </c>
+      <c r="J19">
+        <v>36.41450004577636</v>
+      </c>
+      <c r="K19">
+        <v>32.4218000793457</v>
+      </c>
+      <c r="L19">
+        <v>25.98550004959106</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1.12</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19" t="b">
+        <v>0</v>
+      </c>
+      <c r="V19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>18.75</v>
+      </c>
+      <c r="Y19">
+        <v>39.78</v>
+      </c>
+      <c r="Z19">
+        <v>19.83</v>
+      </c>
+      <c r="AA19">
+        <v>0.26</v>
+      </c>
+      <c r="AB19">
+        <v>98.23999999999999</v>
+      </c>
+      <c r="AC19">
+        <v>167.21</v>
+      </c>
+      <c r="AD19">
         <v>2.01</v>
       </c>
-      <c r="H19">
-        <v>-0.6445144658959856</v>
-      </c>
-      <c r="I19">
-        <v>96.29400024414062</v>
-      </c>
-      <c r="J19">
-        <v>90.30549964904785</v>
-      </c>
-      <c r="K19">
-        <v>87.76579986572266</v>
-      </c>
-      <c r="L19">
-        <v>84.11959991455078</v>
-      </c>
-      <c r="M19">
-        <v>1.07</v>
-      </c>
-      <c r="N19">
-        <v>1.1</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19" t="b">
-        <v>0</v>
-      </c>
-      <c r="V19" t="b">
-        <v>1</v>
-      </c>
-      <c r="W19" t="b">
-        <v>1</v>
-      </c>
-      <c r="X19">
-        <v>61.8</v>
-      </c>
-      <c r="Y19">
-        <v>98.88</v>
-      </c>
-      <c r="Z19">
-        <v>45.29</v>
-      </c>
-      <c r="AA19">
-        <v>11.67</v>
-      </c>
-      <c r="AB19">
-        <v>20.56</v>
-      </c>
-      <c r="AC19">
-        <v>32.37</v>
-      </c>
-      <c r="AD19">
-        <v>4.32</v>
-      </c>
       <c r="AE19">
-        <v>-15.6</v>
+        <v>4000</v>
       </c>
       <c r="AF19">
-        <v>17.2</v>
+        <v>112.5</v>
       </c>
       <c r="AG19">
-        <v>33.81</v>
+        <v>86.89</v>
       </c>
       <c r="AH19" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="AI19" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="AJ19" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="AK19">
-        <v>23.44812327235647</v>
+        <v>52.91803792159791</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2763,49 +2823,49 @@
         <v>55</v>
       </c>
       <c r="B20">
-        <v>92.75653923541248</v>
+        <v>93.36016096579478</v>
       </c>
       <c r="C20">
-        <v>403</v>
+        <v>205</v>
       </c>
       <c r="D20">
-        <v>177.05</v>
+        <v>168.65</v>
       </c>
       <c r="E20">
-        <v>1.83</v>
+        <v>1.43</v>
       </c>
       <c r="F20">
-        <v>-0.6739673273258162</v>
+        <v>-1.090155579829533</v>
       </c>
       <c r="G20">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="H20">
-        <v>-1.26452267833585</v>
+        <v>-0.9879423402843406</v>
       </c>
       <c r="I20">
-        <v>177.6180023193359</v>
+        <v>167.5299987792969</v>
       </c>
       <c r="J20">
-        <v>165.2855003356934</v>
+        <v>160.7279998779297</v>
       </c>
       <c r="K20">
-        <v>159.7123999023437</v>
+        <v>153.6324002075195</v>
       </c>
       <c r="L20">
-        <v>141.0526497650146</v>
+        <v>144.0382996749878</v>
       </c>
       <c r="M20">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N20">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="P20">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -2814,7 +2874,7 @@
         <v>0</v>
       </c>
       <c r="T20">
-        <v>3.888888888888888</v>
+        <v>0</v>
       </c>
       <c r="U20" t="b">
         <v>0</v>
@@ -2826,46 +2886,46 @@
         <v>1</v>
       </c>
       <c r="X20">
-        <v>115.63</v>
+        <v>109.52</v>
       </c>
       <c r="Y20">
-        <v>179.97</v>
+        <v>170.66</v>
       </c>
       <c r="Z20">
-        <v>21.22</v>
+        <v>128.76</v>
       </c>
       <c r="AA20">
-        <v>6.14</v>
+        <v>11.14</v>
       </c>
       <c r="AB20">
-        <v>12.2</v>
+        <v>57.54</v>
       </c>
       <c r="AC20">
-        <v>22.78</v>
+        <v>236</v>
       </c>
       <c r="AD20">
-        <v>8.49</v>
+        <v>3.45</v>
       </c>
       <c r="AE20">
-        <v>-15.97</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="AF20">
-        <v>52.02</v>
+        <v>20.99</v>
       </c>
       <c r="AG20">
-        <v>-3.89</v>
+        <v>62</v>
       </c>
       <c r="AH20" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AJ20" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="AK20">
-        <v>23.22800159381228</v>
+        <v>51.67945550831916</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -2873,43 +2933,43 @@
         <v>56</v>
       </c>
       <c r="B21">
-        <v>97.1830985915493</v>
+        <v>94.76861167002012</v>
       </c>
       <c r="C21">
-        <v>328</v>
+        <v>53</v>
       </c>
       <c r="D21">
-        <v>311.3</v>
+        <v>42.55</v>
       </c>
       <c r="E21">
-        <v>3.12</v>
+        <v>2.84</v>
       </c>
       <c r="F21">
-        <v>0.883621658790363</v>
+        <v>0.5821411029189434</v>
       </c>
       <c r="G21">
-        <v>2.36</v>
+        <v>3.01</v>
       </c>
       <c r="H21">
-        <v>-0.1727690868656537</v>
+        <v>0.6719635272627189</v>
       </c>
       <c r="I21">
-        <v>312.2800048828125</v>
+        <v>41.26199951171875</v>
       </c>
       <c r="J21">
-        <v>301.2180023193359</v>
+        <v>41.24649963378906</v>
       </c>
       <c r="K21">
-        <v>293.031801147461</v>
+        <v>40.54019996643066</v>
       </c>
       <c r="L21">
-        <v>271.1899507904052</v>
+        <v>33.28699990272522</v>
       </c>
       <c r="M21">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="N21">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -2936,46 +2996,46 @@
         <v>1</v>
       </c>
       <c r="X21">
-        <v>179.96</v>
+        <v>24.52</v>
       </c>
       <c r="Y21">
-        <v>318.38</v>
+        <v>46.27</v>
       </c>
       <c r="Z21">
-        <v>75.14</v>
+        <v>42.74</v>
       </c>
       <c r="AA21">
-        <v>180.78</v>
+        <v>-24.78</v>
       </c>
       <c r="AB21">
-        <v>11.99</v>
+        <v>118.21</v>
       </c>
       <c r="AC21">
-        <v>20.6</v>
+        <v>104.76</v>
       </c>
       <c r="AD21">
-        <v>7.14</v>
+        <v>4</v>
       </c>
       <c r="AE21">
-        <v>14.51</v>
+        <v>10.26</v>
       </c>
       <c r="AF21">
-        <v>6.02</v>
+        <v>25.81</v>
       </c>
       <c r="AG21">
-        <v>-0.66</v>
+        <v>47.62</v>
       </c>
       <c r="AH21" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="AI21" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="AJ21" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="AK21">
-        <v>17.21070496973962</v>
+        <v>50.93201675042164</v>
       </c>
     </row>
     <row r="22" spans="1:37">
@@ -2983,49 +3043,49 @@
         <v>57</v>
       </c>
       <c r="B22">
-        <v>90.54325955734407</v>
+        <v>93.76257545271631</v>
       </c>
       <c r="C22">
-        <v>148</v>
+        <v>423</v>
       </c>
       <c r="D22">
-        <v>78.91</v>
+        <v>738.84</v>
       </c>
       <c r="E22">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="F22">
-        <v>-1.446724653771053</v>
+        <v>-1.090155579829533</v>
       </c>
       <c r="G22">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="H22">
-        <v>-1.46669926934885</v>
+        <v>-1.219840954132827</v>
       </c>
       <c r="I22">
-        <v>80.43200073242187</v>
+        <v>711.7759887695313</v>
       </c>
       <c r="J22">
-        <v>78.34350051879883</v>
+        <v>691.1339965820313</v>
       </c>
       <c r="K22">
-        <v>77.4924008178711</v>
+        <v>648.4601989746094</v>
       </c>
       <c r="L22">
-        <v>72.16275018692016</v>
+        <v>623.786750793457</v>
       </c>
       <c r="M22">
         <v>1.03</v>
       </c>
       <c r="N22">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -3034,58 +3094,58 @@
         <v>0</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.888888888888889</v>
       </c>
       <c r="U22" t="b">
         <v>0</v>
       </c>
       <c r="V22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" t="b">
         <v>0</v>
       </c>
       <c r="X22">
-        <v>61.41</v>
+        <v>474.6</v>
       </c>
       <c r="Y22">
-        <v>82.09999999999999</v>
+        <v>747.42</v>
       </c>
       <c r="Z22">
-        <v>46.54</v>
+        <v>70.86</v>
       </c>
       <c r="AA22">
-        <v>7.45</v>
+        <v>12.84</v>
       </c>
       <c r="AB22">
-        <v>0.42</v>
+        <v>76.73</v>
       </c>
       <c r="AC22">
-        <v>39.8</v>
+        <v>97.92</v>
       </c>
       <c r="AD22">
-        <v>7.61</v>
+        <v>11.88</v>
       </c>
       <c r="AE22">
-        <v>0.74</v>
+        <v>36.24</v>
       </c>
       <c r="AF22">
-        <v>24.77</v>
+        <v>-47.92</v>
       </c>
       <c r="AG22">
-        <v>11.22</v>
+        <v>178.92</v>
       </c>
       <c r="AH22" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AI22" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AJ22" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="AK22">
-        <v>3.360065626276355</v>
+        <v>50.84782971718079</v>
       </c>
     </row>
     <row r="23" spans="1:37">
@@ -3093,43 +3153,43 @@
         <v>58</v>
       </c>
       <c r="B23">
-        <v>99.3963782696177</v>
+        <v>90.3420523138833</v>
       </c>
       <c r="C23">
         <v>43</v>
       </c>
       <c r="D23">
-        <v>7.97</v>
+        <v>48.97</v>
       </c>
       <c r="E23">
-        <v>4.86</v>
+        <v>2.66</v>
       </c>
       <c r="F23">
-        <v>2.984555640063349</v>
+        <v>0.368656420014883</v>
       </c>
       <c r="G23">
-        <v>3.99</v>
+        <v>2.76</v>
       </c>
       <c r="H23">
-        <v>2.024216535475607</v>
+        <v>0.3668337721989212</v>
       </c>
       <c r="I23">
-        <v>7.414199924468994</v>
+        <v>49.10000076293945</v>
       </c>
       <c r="J23">
-        <v>6.293399977684021</v>
+        <v>49.08950023651123</v>
       </c>
       <c r="K23">
-        <v>6.190039978027344</v>
+        <v>45.78060020446777</v>
       </c>
       <c r="L23">
-        <v>4.998104989528656</v>
+        <v>39.38020009994507</v>
       </c>
       <c r="M23">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="N23">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -3141,61 +3201,1607 @@
         <v>0</v>
       </c>
       <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23" t="b">
+        <v>0</v>
+      </c>
+      <c r="V23" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" t="b">
+        <v>1</v>
+      </c>
+      <c r="X23">
+        <v>30.02</v>
+      </c>
+      <c r="Y23">
+        <v>51.99</v>
+      </c>
+      <c r="Z23">
+        <v>61.84</v>
+      </c>
+      <c r="AA23">
+        <v>-6.51</v>
+      </c>
+      <c r="AB23">
+        <v>225.56</v>
+      </c>
+      <c r="AC23">
+        <v>53.06</v>
+      </c>
+      <c r="AD23">
+        <v>5.9</v>
+      </c>
+      <c r="AE23">
+        <v>-21.05</v>
+      </c>
+      <c r="AF23">
+        <v>28.38</v>
+      </c>
+      <c r="AG23">
+        <v>51.02</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>92</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>108</v>
+      </c>
+      <c r="AK23">
+        <v>50.65966201746414</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37">
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24">
+        <v>90.94567404426559</v>
+      </c>
+      <c r="C24">
+        <v>87</v>
+      </c>
+      <c r="D24">
+        <v>34.42</v>
+      </c>
+      <c r="E24">
+        <v>1.58</v>
+      </c>
+      <c r="F24">
+        <v>-0.9122516774094818</v>
+      </c>
+      <c r="G24">
+        <v>1.44</v>
+      </c>
+      <c r="H24">
+        <v>-1.244251334537931</v>
+      </c>
+      <c r="I24">
+        <v>33.63600006103515</v>
+      </c>
+      <c r="J24">
+        <v>32.81550006866455</v>
+      </c>
+      <c r="K24">
+        <v>31.70040008544922</v>
+      </c>
+      <c r="L24">
+        <v>27.91335003852844</v>
+      </c>
+      <c r="M24">
+        <v>1.03</v>
+      </c>
+      <c r="N24">
+        <v>1.06</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24" t="b">
+        <v>1</v>
+      </c>
+      <c r="V24" t="b">
+        <v>1</v>
+      </c>
+      <c r="W24" t="b">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>23.21</v>
+      </c>
+      <c r="Y24">
+        <v>34.52</v>
+      </c>
+      <c r="Z24">
+        <v>31.72</v>
+      </c>
+      <c r="AA24">
+        <v>-1736.11</v>
+      </c>
+      <c r="AB24">
+        <v>140.38</v>
+      </c>
+      <c r="AC24">
+        <v>45.71</v>
+      </c>
+      <c r="AD24">
+        <v>4.49</v>
+      </c>
+      <c r="AE24">
+        <v>264.29</v>
+      </c>
+      <c r="AF24">
+        <v>-44</v>
+      </c>
+      <c r="AG24">
+        <v>-28.57</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>109</v>
+      </c>
+      <c r="AK24">
+        <v>46.38400789784454</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37">
+      <c r="A25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25">
+        <v>94.36619718309859</v>
+      </c>
+      <c r="C25">
+        <v>59</v>
+      </c>
+      <c r="D25">
+        <v>50.13</v>
+      </c>
+      <c r="E25">
+        <v>1.15</v>
+      </c>
+      <c r="F25">
+        <v>-1.42224286434696</v>
+      </c>
+      <c r="G25">
+        <v>1.24</v>
+      </c>
+      <c r="H25">
+        <v>-1.488355138588969</v>
+      </c>
+      <c r="I25">
+        <v>49</v>
+      </c>
+      <c r="J25">
+        <v>45.94900016784668</v>
+      </c>
+      <c r="K25">
+        <v>43.89907241821289</v>
+      </c>
+      <c r="L25">
+        <v>38.21824165344238</v>
+      </c>
+      <c r="M25">
+        <v>1.07</v>
+      </c>
+      <c r="N25">
+        <v>1.12</v>
+      </c>
+      <c r="O25" t="s">
+        <v>73</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="Q25">
         <v>2</v>
       </c>
-      <c r="T23">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="U23" t="b">
-        <v>0</v>
-      </c>
-      <c r="V23" t="b">
-        <v>1</v>
-      </c>
-      <c r="W23" t="b">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>3.41</v>
-      </c>
-      <c r="Y23">
-        <v>8.6</v>
-      </c>
-      <c r="Z23">
-        <v>3.03</v>
-      </c>
-      <c r="AA23">
-        <v>1270.81</v>
-      </c>
-      <c r="AB23">
-        <v>185</v>
-      </c>
-      <c r="AC23">
-        <v>328.05</v>
-      </c>
-      <c r="AD23">
-        <v>11.35</v>
-      </c>
-      <c r="AE23">
-        <v>28.57</v>
-      </c>
-      <c r="AF23">
-        <v>83.22</v>
-      </c>
-      <c r="AG23">
-        <v>81.70999999999999</v>
-      </c>
-      <c r="AH23" t="s">
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>2.777777777777778</v>
+      </c>
+      <c r="U25" t="b">
+        <v>0</v>
+      </c>
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+      <c r="W25" t="b">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>30.53</v>
+      </c>
+      <c r="Y25">
+        <v>50.29</v>
+      </c>
+      <c r="Z25">
+        <v>40.37</v>
+      </c>
+      <c r="AA25">
+        <v>6.69</v>
+      </c>
+      <c r="AB25">
+        <v>1.75</v>
+      </c>
+      <c r="AC25">
+        <v>233.33</v>
+      </c>
+      <c r="AD25">
+        <v>0.89</v>
+      </c>
+      <c r="AE25">
+        <v>-67.48</v>
+      </c>
+      <c r="AF25">
+        <v>200</v>
+      </c>
+      <c r="AG25">
+        <v>236.67</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>110</v>
+      </c>
+      <c r="AK25">
+        <v>32.89130871323124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:37">
+      <c r="A26" t="s">
         <v>61</v>
       </c>
-      <c r="AI23" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ23" t="s">
+      <c r="B26">
+        <v>91.34808853118712</v>
+      </c>
+      <c r="C26">
+        <v>320</v>
+      </c>
+      <c r="D26">
+        <v>55.93</v>
+      </c>
+      <c r="E26">
+        <v>1.64</v>
+      </c>
+      <c r="F26">
+        <v>-0.8410901164414617</v>
+      </c>
+      <c r="G26">
+        <v>2.07</v>
+      </c>
+      <c r="H26">
+        <v>-0.4753243517771605</v>
+      </c>
+      <c r="I26">
+        <v>55.77000045776367</v>
+      </c>
+      <c r="J26">
+        <v>52.93450031280518</v>
+      </c>
+      <c r="K26">
+        <v>49.28439994812012</v>
+      </c>
+      <c r="L26">
+        <v>46.82329999923706</v>
+      </c>
+      <c r="M26">
+        <v>1.05</v>
+      </c>
+      <c r="N26">
+        <v>1.13</v>
+      </c>
+      <c r="P26">
+        <v>3</v>
+      </c>
+      <c r="Q26">
+        <v>1</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>2.777777777777778</v>
+      </c>
+      <c r="U26" t="b">
+        <v>1</v>
+      </c>
+      <c r="V26" t="b">
+        <v>1</v>
+      </c>
+      <c r="W26" t="b">
+        <v>1</v>
+      </c>
+      <c r="X26">
+        <v>37.65</v>
+      </c>
+      <c r="Y26">
+        <v>56.51</v>
+      </c>
+      <c r="Z26">
+        <v>15.23</v>
+      </c>
+      <c r="AA26">
+        <v>73.84999999999999</v>
+      </c>
+      <c r="AB26">
+        <v>15.56</v>
+      </c>
+      <c r="AC26">
+        <v>37.5</v>
+      </c>
+      <c r="AD26">
+        <v>7.17</v>
+      </c>
+      <c r="AE26">
+        <v>-4.35</v>
+      </c>
+      <c r="AF26">
+        <v>-75.79000000000001</v>
+      </c>
+      <c r="AG26">
+        <v>493.75</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI26" t="s">
         <v>93</v>
       </c>
-      <c r="AK23">
-        <v>56.90937360648951</v>
+      <c r="AJ26" t="s">
+        <v>111</v>
+      </c>
+      <c r="AK26">
+        <v>32.62204907207411</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37">
+      <c r="A27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27">
+        <v>93.56136820925553</v>
+      </c>
+      <c r="C27">
+        <v>233</v>
+      </c>
+      <c r="D27">
+        <v>112.89</v>
+      </c>
+      <c r="E27">
+        <v>2.33</v>
+      </c>
+      <c r="F27">
+        <v>-0.02273216530922856</v>
+      </c>
+      <c r="G27">
+        <v>2.1</v>
+      </c>
+      <c r="H27">
+        <v>-0.4387087811695045</v>
+      </c>
+      <c r="I27">
+        <v>109.0519989013672</v>
+      </c>
+      <c r="J27">
+        <v>104.4399997711182</v>
+      </c>
+      <c r="K27">
+        <v>99.14300003051758</v>
+      </c>
+      <c r="L27">
+        <v>83.93800012588501</v>
+      </c>
+      <c r="M27">
+        <v>1.04</v>
+      </c>
+      <c r="N27">
+        <v>1.1</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27" t="b">
+        <v>0</v>
+      </c>
+      <c r="V27" t="b">
+        <v>1</v>
+      </c>
+      <c r="W27" t="b">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>61.93</v>
+      </c>
+      <c r="Y27">
+        <v>113.78</v>
+      </c>
+      <c r="Z27">
+        <v>22.9</v>
+      </c>
+      <c r="AA27">
+        <v>-0.08</v>
+      </c>
+      <c r="AB27">
+        <v>119.51</v>
+      </c>
+      <c r="AC27">
+        <v>6.1</v>
+      </c>
+      <c r="AD27">
+        <v>5.07</v>
+      </c>
+      <c r="AE27">
+        <v>135.14</v>
+      </c>
+      <c r="AF27">
+        <v>254.17</v>
+      </c>
+      <c r="AG27">
+        <v>-129.27</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>85</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK27">
+        <v>32.08677581762093</v>
+      </c>
+    </row>
+    <row r="28" spans="1:37">
+      <c r="A28" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28">
+        <v>94.16498993963782</v>
+      </c>
+      <c r="C28">
+        <v>433</v>
+      </c>
+      <c r="D28">
+        <v>408.95</v>
+      </c>
+      <c r="E28">
+        <v>1.43</v>
+      </c>
+      <c r="F28">
+        <v>-1.090155579829533</v>
+      </c>
+      <c r="G28">
+        <v>1.57</v>
+      </c>
+      <c r="H28">
+        <v>-1.085583861904756</v>
+      </c>
+      <c r="I28">
+        <v>403.3100036621094</v>
+      </c>
+      <c r="J28">
+        <v>381.943000793457</v>
+      </c>
+      <c r="K28">
+        <v>369.2492010498047</v>
+      </c>
+      <c r="L28">
+        <v>337.9261012268066</v>
+      </c>
+      <c r="M28">
+        <v>1.06</v>
+      </c>
+      <c r="N28">
+        <v>1.09</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28" t="b">
+        <v>0</v>
+      </c>
+      <c r="V28" t="b">
+        <v>1</v>
+      </c>
+      <c r="W28" t="b">
+        <v>1</v>
+      </c>
+      <c r="X28">
+        <v>261.17</v>
+      </c>
+      <c r="Y28">
+        <v>411.89</v>
+      </c>
+      <c r="Z28">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="AA28">
+        <v>2.77</v>
+      </c>
+      <c r="AB28">
+        <v>16.59</v>
+      </c>
+      <c r="AC28">
+        <v>44.34</v>
+      </c>
+      <c r="AD28">
+        <v>11.84</v>
+      </c>
+      <c r="AE28">
+        <v>26.09</v>
+      </c>
+      <c r="AF28">
+        <v>27.78</v>
+      </c>
+      <c r="AG28">
+        <v>-10.41</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ28" t="s">
+        <v>106</v>
+      </c>
+      <c r="AK28">
+        <v>31.80270058340951</v>
+      </c>
+    </row>
+    <row r="29" spans="1:37">
+      <c r="A29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29">
+        <v>95.17102615694165</v>
+      </c>
+      <c r="C29">
+        <v>77</v>
+      </c>
+      <c r="D29">
+        <v>174.96</v>
+      </c>
+      <c r="E29">
+        <v>1.15</v>
+      </c>
+      <c r="F29">
+        <v>-1.42224286434696</v>
+      </c>
+      <c r="G29">
+        <v>1.15</v>
+      </c>
+      <c r="H29">
+        <v>-1.598201850411936</v>
+      </c>
+      <c r="I29">
+        <v>168.4940002441406</v>
+      </c>
+      <c r="J29">
+        <v>161.8534996032715</v>
+      </c>
+      <c r="K29">
+        <v>151.6453988647461</v>
+      </c>
+      <c r="L29">
+        <v>126.676199760437</v>
+      </c>
+      <c r="M29">
+        <v>1.04</v>
+      </c>
+      <c r="N29">
+        <v>1.11</v>
+      </c>
+      <c r="P29">
+        <v>3</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="U29" t="b">
+        <v>0</v>
+      </c>
+      <c r="V29" t="b">
+        <v>1</v>
+      </c>
+      <c r="W29" t="b">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>105.56</v>
+      </c>
+      <c r="Y29">
+        <v>175.91</v>
+      </c>
+      <c r="Z29">
+        <v>240.61</v>
+      </c>
+      <c r="AA29">
+        <v>5.82</v>
+      </c>
+      <c r="AB29">
+        <v>37</v>
+      </c>
+      <c r="AC29">
+        <v>14</v>
+      </c>
+      <c r="AD29">
+        <v>26.2</v>
+      </c>
+      <c r="AE29">
+        <v>28.09</v>
+      </c>
+      <c r="AF29">
+        <v>323.81</v>
+      </c>
+      <c r="AG29">
+        <v>-79</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>112</v>
+      </c>
+      <c r="AK29">
+        <v>30.79511712790917</v>
+      </c>
+    </row>
+    <row r="30" spans="1:37">
+      <c r="A30" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30">
+        <v>93.158953722334</v>
+      </c>
+      <c r="C30">
+        <v>440</v>
+      </c>
+      <c r="D30">
+        <v>213.71</v>
+      </c>
+      <c r="E30">
+        <v>1.72</v>
+      </c>
+      <c r="F30">
+        <v>-0.7462080351507679</v>
+      </c>
+      <c r="G30">
+        <v>1.74</v>
+      </c>
+      <c r="H30">
+        <v>-0.8780956284613733</v>
+      </c>
+      <c r="I30">
+        <v>210.2200012207031</v>
+      </c>
+      <c r="J30">
+        <v>201.3845016479492</v>
+      </c>
+      <c r="K30">
+        <v>197.9866003417969</v>
+      </c>
+      <c r="L30">
+        <v>191.2250999450684</v>
+      </c>
+      <c r="M30">
+        <v>1.04</v>
+      </c>
+      <c r="N30">
+        <v>1.06</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V30" t="b">
+        <v>1</v>
+      </c>
+      <c r="W30" t="b">
+        <v>1</v>
+      </c>
+      <c r="X30">
+        <v>138.58</v>
+      </c>
+      <c r="Y30">
+        <v>228.84</v>
+      </c>
+      <c r="Z30">
+        <v>31.75</v>
+      </c>
+      <c r="AA30">
+        <v>9.73</v>
+      </c>
+      <c r="AB30">
+        <v>18.1</v>
+      </c>
+      <c r="AC30">
+        <v>29.87</v>
+      </c>
+      <c r="AD30">
+        <v>7.5</v>
+      </c>
+      <c r="AE30">
+        <v>41.84</v>
+      </c>
+      <c r="AF30">
+        <v>12.8</v>
+      </c>
+      <c r="AG30">
+        <v>-18.83</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>106</v>
+      </c>
+      <c r="AK30">
+        <v>29.67805515025601</v>
+      </c>
+    </row>
+    <row r="31" spans="1:37">
+      <c r="A31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31">
+        <v>97.1830985915493</v>
+      </c>
+      <c r="C31">
+        <v>85</v>
+      </c>
+      <c r="D31">
+        <v>101.37</v>
+      </c>
+      <c r="E31">
+        <v>2.04</v>
+      </c>
+      <c r="F31">
+        <v>-0.3666797099879932</v>
+      </c>
+      <c r="G31">
+        <v>3.35</v>
+      </c>
+      <c r="H31">
+        <v>1.086939994149484</v>
+      </c>
+      <c r="I31">
+        <v>102.6913330078125</v>
+      </c>
+      <c r="J31">
+        <v>99.62966613769531</v>
+      </c>
+      <c r="K31">
+        <v>92.69766647338867</v>
+      </c>
+      <c r="L31">
+        <v>82.23472507476806</v>
+      </c>
+      <c r="M31">
+        <v>1.03</v>
+      </c>
+      <c r="N31">
+        <v>1.11</v>
+      </c>
+      <c r="P31">
+        <v>1</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0.5555555555555555</v>
+      </c>
+      <c r="U31" t="b">
+        <v>1</v>
+      </c>
+      <c r="V31" t="b">
+        <v>0</v>
+      </c>
+      <c r="W31" t="b">
+        <v>1</v>
+      </c>
+      <c r="X31">
+        <v>53.71</v>
+      </c>
+      <c r="Y31">
+        <v>105.98</v>
+      </c>
+      <c r="Z31">
+        <v>25.4</v>
+      </c>
+      <c r="AA31">
+        <v>30.64</v>
+      </c>
+      <c r="AB31">
+        <v>11.05</v>
+      </c>
+      <c r="AC31">
+        <v>36</v>
+      </c>
+      <c r="AD31">
+        <v>-79.37</v>
+      </c>
+      <c r="AE31">
+        <v>8.57</v>
+      </c>
+      <c r="AF31">
+        <v>15.32</v>
+      </c>
+      <c r="AG31">
+        <v>17.34</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI31" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK31">
+        <v>28.24640119646831</v>
+      </c>
+    </row>
+    <row r="32" spans="1:37">
+      <c r="A32" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32">
+        <v>99.59758551307847</v>
+      </c>
+      <c r="C32">
+        <v>75</v>
+      </c>
+      <c r="D32">
+        <v>43.02</v>
+      </c>
+      <c r="E32">
+        <v>2.9</v>
+      </c>
+      <c r="F32">
+        <v>0.6533026638869637</v>
+      </c>
+      <c r="G32">
+        <v>2.92</v>
+      </c>
+      <c r="H32">
+        <v>0.5621168154397519</v>
+      </c>
+      <c r="I32">
+        <v>41.9</v>
+      </c>
+      <c r="J32">
+        <v>40.45750007629395</v>
+      </c>
+      <c r="K32">
+        <v>37.08179996490478</v>
+      </c>
+      <c r="L32">
+        <v>27.11850004196167</v>
+      </c>
+      <c r="M32">
+        <v>1.04</v>
+      </c>
+      <c r="N32">
+        <v>1.13</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32" t="b">
+        <v>0</v>
+      </c>
+      <c r="V32" t="b">
+        <v>1</v>
+      </c>
+      <c r="W32" t="b">
+        <v>1</v>
+      </c>
+      <c r="X32">
+        <v>15.55</v>
+      </c>
+      <c r="Y32">
+        <v>43.88</v>
+      </c>
+      <c r="Z32">
+        <v>10.08</v>
+      </c>
+      <c r="AA32">
+        <v>-5.24</v>
+      </c>
+      <c r="AB32">
+        <v>121.96</v>
+      </c>
+      <c r="AC32">
+        <v>2.94</v>
+      </c>
+      <c r="AD32">
+        <v>-67.64</v>
+      </c>
+      <c r="AE32">
+        <v>450</v>
+      </c>
+      <c r="AF32">
+        <v>-136.14</v>
+      </c>
+      <c r="AG32">
+        <v>-18.63</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK32">
+        <v>28.10045096861539</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37">
+      <c r="A33" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33">
+        <v>90.14084507042254</v>
+      </c>
+      <c r="C33">
+        <v>202</v>
+      </c>
+      <c r="D33">
+        <v>139.29</v>
+      </c>
+      <c r="E33">
+        <v>1.31</v>
+      </c>
+      <c r="F33">
+        <v>-1.232478701765573</v>
+      </c>
+      <c r="G33">
+        <v>1.74</v>
+      </c>
+      <c r="H33">
+        <v>-0.8780956284613733</v>
+      </c>
+      <c r="I33">
+        <v>139.7839965820312</v>
+      </c>
+      <c r="J33">
+        <v>131.4749992370606</v>
+      </c>
+      <c r="K33">
+        <v>124.1059999084473</v>
+      </c>
+      <c r="L33">
+        <v>119.8863501358032</v>
+      </c>
+      <c r="M33">
+        <v>1.06</v>
+      </c>
+      <c r="N33">
+        <v>1.13</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>1</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="U33" t="b">
+        <v>0</v>
+      </c>
+      <c r="V33" t="b">
+        <v>1</v>
+      </c>
+      <c r="W33" t="b">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="Y33">
+        <v>141.92</v>
+      </c>
+      <c r="Z33">
+        <v>43.27</v>
+      </c>
+      <c r="AA33">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="AB33">
+        <v>3.01</v>
+      </c>
+      <c r="AC33">
+        <v>63.01</v>
+      </c>
+      <c r="AD33">
+        <v>13.11</v>
+      </c>
+      <c r="AE33">
+        <v>29.35</v>
+      </c>
+      <c r="AF33">
+        <v>-1.08</v>
+      </c>
+      <c r="AG33">
+        <v>27.4</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>114</v>
+      </c>
+      <c r="AK33">
+        <v>24.9741262026709</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37">
+      <c r="A34" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34">
+        <v>95.57344064386318</v>
+      </c>
+      <c r="C34">
+        <v>156</v>
+      </c>
+      <c r="D34">
+        <v>95.25</v>
+      </c>
+      <c r="E34">
+        <v>1.97</v>
+      </c>
+      <c r="F34">
+        <v>-0.4497015311173502</v>
+      </c>
+      <c r="G34">
+        <v>1.77</v>
+      </c>
+      <c r="H34">
+        <v>-0.8414800578537176</v>
+      </c>
+      <c r="I34">
+        <v>92.67800140380859</v>
+      </c>
+      <c r="J34">
+        <v>88.8314998626709</v>
+      </c>
+      <c r="K34">
+        <v>82.43619995117187</v>
+      </c>
+      <c r="L34">
+        <v>67.98844985961914</v>
+      </c>
+      <c r="M34">
+        <v>1.04</v>
+      </c>
+      <c r="N34">
+        <v>1.12</v>
+      </c>
+      <c r="O34" t="s">
+        <v>73</v>
+      </c>
+      <c r="P34">
+        <v>5</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>2.777777777777778</v>
+      </c>
+      <c r="U34" t="b">
+        <v>0</v>
+      </c>
+      <c r="V34" t="b">
+        <v>1</v>
+      </c>
+      <c r="W34" t="b">
+        <v>1</v>
+      </c>
+      <c r="X34">
+        <v>56.91</v>
+      </c>
+      <c r="Y34">
+        <v>96.03</v>
+      </c>
+      <c r="Z34">
+        <v>38.26</v>
+      </c>
+      <c r="AA34">
+        <v>12.51</v>
+      </c>
+      <c r="AB34">
+        <v>9.59</v>
+      </c>
+      <c r="AC34">
+        <v>13.93</v>
+      </c>
+      <c r="AD34">
+        <v>3.54</v>
+      </c>
+      <c r="AE34">
+        <v>49.46</v>
+      </c>
+      <c r="AF34">
+        <v>-26.19</v>
+      </c>
+      <c r="AG34">
+        <v>3.28</v>
+      </c>
+      <c r="AH34" t="s">
+        <v>83</v>
+      </c>
+      <c r="AI34" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>115</v>
+      </c>
+      <c r="AK34">
+        <v>22.90345504547053</v>
+      </c>
+    </row>
+    <row r="35" spans="1:37">
+      <c r="A35" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35">
+        <v>96.98189134808854</v>
+      </c>
+      <c r="C35">
+        <v>139</v>
+      </c>
+      <c r="D35">
+        <v>67.17</v>
+      </c>
+      <c r="E35">
+        <v>2.52</v>
+      </c>
+      <c r="F35">
+        <v>0.2026127777561689</v>
+      </c>
+      <c r="G35">
+        <v>3.79</v>
+      </c>
+      <c r="H35">
+        <v>1.623968363061768</v>
+      </c>
+      <c r="I35">
+        <v>67.78399963378907</v>
+      </c>
+      <c r="J35">
+        <v>65.13130016326905</v>
+      </c>
+      <c r="K35">
+        <v>63.26324035644532</v>
+      </c>
+      <c r="L35">
+        <v>61.86361013412476</v>
+      </c>
+      <c r="M35">
+        <v>1.04</v>
+      </c>
+      <c r="N35">
+        <v>1.07</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35" t="b">
+        <v>1</v>
+      </c>
+      <c r="V35" t="b">
+        <v>0</v>
+      </c>
+      <c r="W35" t="b">
+        <v>1</v>
+      </c>
+      <c r="X35">
+        <v>38.56</v>
+      </c>
+      <c r="Y35">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="Z35">
+        <v>60.04</v>
+      </c>
+      <c r="AA35">
+        <v>5920</v>
+      </c>
+      <c r="AB35">
+        <v>1.09</v>
+      </c>
+      <c r="AC35">
+        <v>80.3</v>
+      </c>
+      <c r="AD35">
+        <v>24.9</v>
+      </c>
+      <c r="AE35">
+        <v>19</v>
+      </c>
+      <c r="AF35">
+        <v>17.65</v>
+      </c>
+      <c r="AG35">
+        <v>28.79</v>
+      </c>
+      <c r="AH35" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI35" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK35">
+        <v>21.20276076584865</v>
+      </c>
+    </row>
+    <row r="36" spans="1:37">
+      <c r="A36" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36">
+        <v>96.17706237424547</v>
+      </c>
+      <c r="C36">
+        <v>76</v>
+      </c>
+      <c r="D36">
+        <v>32.76</v>
+      </c>
+      <c r="E36">
+        <v>2.87</v>
+      </c>
+      <c r="F36">
+        <v>0.6177218834029539</v>
+      </c>
+      <c r="G36">
+        <v>2.75</v>
+      </c>
+      <c r="H36">
+        <v>0.3546285819963695</v>
+      </c>
+      <c r="I36">
+        <v>33.98400039672852</v>
+      </c>
+      <c r="J36">
+        <v>33.41987495422363</v>
+      </c>
+      <c r="K36">
+        <v>31.76615001678467</v>
+      </c>
+      <c r="L36">
+        <v>28.15347812652588</v>
+      </c>
+      <c r="M36">
+        <v>1.02</v>
+      </c>
+      <c r="N36">
+        <v>1.07</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>1</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="U36" t="b">
+        <v>0</v>
+      </c>
+      <c r="V36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W36" t="b">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>18.91</v>
+      </c>
+      <c r="Y36">
+        <v>37.14</v>
+      </c>
+      <c r="Z36">
+        <v>11.47</v>
+      </c>
+      <c r="AA36">
+        <v>60.09</v>
+      </c>
+      <c r="AB36">
+        <v>2.24</v>
+      </c>
+      <c r="AC36">
+        <v>32.2</v>
+      </c>
+      <c r="AD36">
+        <v>6.01</v>
+      </c>
+      <c r="AE36">
+        <v>6.85</v>
+      </c>
+      <c r="AF36">
+        <v>14.06</v>
+      </c>
+      <c r="AG36">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI36" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>116</v>
+      </c>
+      <c r="AK36">
+        <v>18.90524138511865</v>
+      </c>
+    </row>
+    <row r="37" spans="1:37">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37">
+        <v>96.579476861167</v>
+      </c>
+      <c r="C37">
+        <v>55</v>
+      </c>
+      <c r="D37">
+        <v>28.75</v>
+      </c>
+      <c r="E37">
+        <v>3.71</v>
+      </c>
+      <c r="F37">
+        <v>1.613983736955237</v>
+      </c>
+      <c r="G37">
+        <v>3.13</v>
+      </c>
+      <c r="H37">
+        <v>0.8184258096933419</v>
+      </c>
+      <c r="I37">
+        <v>26.99799995422363</v>
+      </c>
+      <c r="J37">
+        <v>26.21300001144409</v>
+      </c>
+      <c r="K37">
+        <v>24.70439998626709</v>
+      </c>
+      <c r="L37">
+        <v>20.55195001125336</v>
+      </c>
+      <c r="M37">
+        <v>1.03</v>
+      </c>
+      <c r="N37">
+        <v>1.09</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>1</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="U37" t="b">
+        <v>0</v>
+      </c>
+      <c r="V37" t="b">
+        <v>1</v>
+      </c>
+      <c r="W37" t="b">
+        <v>1</v>
+      </c>
+      <c r="X37">
+        <v>14.28</v>
+      </c>
+      <c r="Y37">
+        <v>29.49</v>
+      </c>
+      <c r="Z37">
+        <v>9.58</v>
+      </c>
+      <c r="AA37">
+        <v>-99.48</v>
+      </c>
+      <c r="AB37">
+        <v>180.49</v>
+      </c>
+      <c r="AC37">
+        <v>443.75</v>
+      </c>
+      <c r="AD37">
+        <v>7.99</v>
+      </c>
+      <c r="AE37">
+        <v>987.5</v>
+      </c>
+      <c r="AF37">
+        <v>100</v>
+      </c>
+      <c r="AG37">
+        <v>-75</v>
+      </c>
+      <c r="AH37" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK37">
+        <v>64.84404673313264</v>
       </c>
     </row>
   </sheetData>
